--- a/3_resultados/atributos_seleccionados_rf.xlsx
+++ b/3_resultados/atributos_seleccionados_rf.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B227"/>
+  <dimension ref="A1:B204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,1201 +431,1201 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>roll_mean_3</t>
+          <t>hum_esp_anomalia</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6371205249192448</v>
+        <v>0.2452845064278026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>roll_max_3</t>
+          <t>soi_min_12</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.109742099294019</v>
+        <v>0.1285701341627864</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>roll_min_3</t>
+          <t>sst_max_12</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09027664845839972</v>
+        <v>0.1176533921921825</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>es_pico</t>
+          <t>sst_min_6</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0780533176958912</v>
+        <v>0.03361814080524847</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>roll_max_5</t>
+          <t>sst_anomalia</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01654928686970417</v>
+        <v>0.02181639622129038</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pct_change_2</t>
+          <t>hum_esp_lag_12</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005136943297762514</v>
+        <v>0.01515302359345671</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>diff_1</t>
+          <t>dias_lluvia_acum_12</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.004824147437436433</v>
+        <v>0.01442572469180154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>diff_2</t>
+          <t>hum_rel_anomalia</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004011196465553206</v>
+        <v>0.01148631850764395</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ratio_lag1</t>
+          <t>temp_min</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003162528684647699</v>
+        <v>0.0108662615542897</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>diff_3</t>
+          <t>hum_esp_lag_10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.003125282001703438</v>
+        <v>0.009505468917428156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>estacionalidad_diff_lag_16</t>
+          <t>hum_esp_lag_8</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.002420684283952414</v>
+        <v>0.008677139247650199</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>estacionalidad_diff_lag_4</t>
+          <t>temp_min_clima_semana</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.002388422241194965</v>
+        <v>0.008240012188213849</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>estacionalidad_diff_lag_20</t>
+          <t>sst</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.00210210691437916</v>
+        <v>0.008152559223626609</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>temp_min_lag_3</t>
+          <t>hum_esp_lag_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.001534657569210812</v>
+        <v>0.007504213171040419</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vel_vi_lag_3</t>
+          <t>prec_acum_12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.001510528477541506</v>
+        <v>0.006006343264881317</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pct_change_1</t>
+          <t>soi_avg_12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001485436654689965</v>
+        <v>0.005962988323023764</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>temp_lag_9</t>
+          <t>hum_esp_lag_9</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0009783095044340624</v>
+        <v>0.005636035472276488</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>prec_lag_1</t>
+          <t>vel_vi_max_lag_4</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0008931301756423558</v>
+        <v>0.00555672713961146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>soi_x_tendencia</t>
+          <t>vel_vi_lag_1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0007559025976578075</v>
+        <v>0.005534504429852833</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>prec_lag_4</t>
+          <t>soi_max_12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0006370144467885356</v>
+        <v>0.005228486715612235</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hum_rel_lag_9</t>
+          <t>hum_rel_lag_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0006080762631826305</v>
+        <v>0.00515350430940334</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_5</t>
+          <t>temp_min_lag_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0005883732064412869</v>
+        <v>0.005088786949914433</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>soi_lag_5</t>
+          <t>hum_rel_lag_6</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0005613665781258603</v>
+        <v>0.005035913642323949</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>roll_mean_7</t>
+          <t>sst_lag_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0005304122269745851</v>
+        <v>0.005021049695016376</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>temp_lag_5</t>
+          <t>prec_clima_semana</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0005064200388375365</v>
+        <v>0.004937245663832282</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_2</t>
+          <t>vel_vi_min_lag_10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0005036542875342576</v>
+        <v>0.004797770184422227</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>estacionalidad_diff_lag_24</t>
+          <t>soi_lag_6</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.000485900604712519</v>
+        <v>0.004706624955176446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>roll_mean_5</t>
+          <t>sst_lag_12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0004713140454732197</v>
+        <v>0.004493595162676285</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hum_rel_lag_10</t>
+          <t>temp_max_lag_10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0004708999392810529</v>
+        <v>0.004374787283289443</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>temp_lag_10</t>
+          <t>prec_acum_8</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0004621331445247825</v>
+        <v>0.004306280782017992</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>temp_min_lag_2</t>
+          <t>hum_rel_lag_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0004556849972069559</v>
+        <v>0.004301884234647948</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>temp_max_lag_10</t>
+          <t>temp_min_lag_1</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0004458202183490881</v>
+        <v>0.004298348489679546</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>vel_vi_lag_1</t>
+          <t>sst_min_12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0004452955537811462</v>
+        <v>0.004281580648783155</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_10</t>
+          <t>sst_avg_6</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0004359255881241562</v>
+        <v>0.004157756965387886</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>prec_lag_3</t>
+          <t>vel_vi_max_lag_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0004249716680435944</v>
+        <v>0.004111586934946371</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>vel_vi_lag_8</t>
+          <t>temp_min_lag_3</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.000421334330724746</v>
+        <v>0.004087841567016287</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_2</t>
+          <t>sst_lag_11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.0004056565691884459</v>
+        <v>0.004022661495818723</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_1</t>
+          <t>vel_vi_lag_2</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0003886945930979851</v>
+        <v>0.003924491986934801</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_3</t>
+          <t>hum_esp_lag_3</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0003880605259123654</v>
+        <v>0.003893154020255264</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>soi_lag_3</t>
+          <t>vel_vi_max_lag_1</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0003750294176008471</v>
+        <v>0.003827595963803719</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>roll_std_3</t>
+          <t>vel_vi_max_lag_3</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0003745135247535541</v>
+        <v>0.00368921964390608</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>temp_lag_4</t>
+          <t>vel_vi_max_lag_7</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0003610150260602817</v>
+        <v>0.00359557106558031</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>estacionalidad_diff_lag_12</t>
+          <t>sst_max_6</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0003551409811757886</v>
+        <v>0.003589566138529125</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sst</t>
+          <t>sst_avg_12</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0003510567575782208</v>
+        <v>0.00344936758942197</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>estacionalidad_diff_lag_8</t>
+          <t>prec_lag_12</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0003505552020796836</v>
+        <v>0.003333137613651332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>roll_min_5</t>
+          <t>vel_vi_max_anomalia</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0003451438252399487</v>
+        <v>0.003332202256076602</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>soi_lag_11</t>
+          <t>indice_vectorial</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0003448826314965502</v>
+        <v>0.003043035471158356</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sst_lag_2</t>
+          <t>temp_lag_3</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0003345573734296346</v>
+        <v>0.002898372884916107</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sst_lag_1</t>
+          <t>temp_x_hum_rel</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0003257842953323041</v>
+        <v>0.002874888966278785</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>prec_x_tendencia</t>
+          <t>vel_vi_max_lag_2</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0003240151997210097</v>
+        <v>0.002830992214398192</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>soi_x_casos_lag1</t>
+          <t>vel_vi_lag_3</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.000318887737426827</v>
+        <v>0.002824584858872356</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_6</t>
+          <t>soi_min_6</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0003172819970605727</v>
+        <v>0.002817446645603709</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>temp_max_lag_12</t>
+          <t>sst_lag_2</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0003119348150011058</v>
+        <v>0.002803587089717393</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hum_rel_lag_12</t>
+          <t>vel_vi_lag_4</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0003113483890847924</v>
+        <v>0.002784325459797237</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_4</t>
+          <t>sst_clima_semana</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0003095714794418787</v>
+        <v>0.002760185995217932</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>vel_vi_lag_2</t>
+          <t>hum_rel_lag_7</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0003080099776802401</v>
+        <v>0.002745154669796634</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hum_rel</t>
+          <t>prec_lag_9</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0002925694164027577</v>
+        <v>0.002740985874259597</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_4</t>
+          <t>soi_lag_4</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0002881760490625627</v>
+        <v>0.002697534543141464</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sst_lag_10</t>
+          <t>prec_lag_6</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.000281102092557212</v>
+        <v>0.002663533441884066</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_11</t>
+          <t>vel_vi_lag_12</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0002779503526657383</v>
+        <v>0.002627957013868101</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>soi</t>
+          <t>temp_max_lag_7</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0002710246604756867</v>
+        <v>0.002560078641779013</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_3</t>
+          <t>vel_vi</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0002675264663779138</v>
+        <v>0.002550534711862848</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>prec_lag_10</t>
+          <t>hum_esp_lag_4</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0002666091142358048</v>
+        <v>0.002476570592922779</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>prec_lag_6</t>
+          <t>sst_lag_3</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0002541434659051773</v>
+        <v>0.0024746764390075</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>estacionalidad_lag_24</t>
+          <t>sst_lag_10</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0002516273593460857</v>
+        <v>0.002456355423861834</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>hum_esp_lag_2</t>
+          <t>temp_lag_7</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.0002462201451701788</v>
+        <v>0.002393648185416407</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>temp_max_lag_9</t>
+          <t>vel_vi_lag_5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.0002442050535466582</v>
+        <v>0.002368136395619907</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>temp_lag_8</t>
+          <t>hum_rel_lag_11</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0002390868662467638</v>
+        <v>0.002286571565678055</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_9</t>
+          <t>dias_lluvia_anomalia</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.0002334323509095673</v>
+        <v>0.002276211187671515</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>temp_max</t>
+          <t>sst_lag_4</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.0002302555774183343</v>
+        <v>0.002256496350610852</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>soi_lag_9</t>
+          <t>vel_vi_anomalia</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0002233157167439881</v>
+        <v>0.002229891475395674</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>hum_esp</t>
+          <t>dias_lluvia_clima_semana</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.000218672983417157</v>
+        <v>0.002217381841542494</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>roll_std_26</t>
+          <t>soi</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0002058065409412957</v>
+        <v>0.00218360734380389</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>vel_vi_lag_11</t>
+          <t>sst_lag_6</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.0002032940598911235</v>
+        <v>0.002169151576791163</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>prec_lag_12</t>
+          <t>hum_rel_lag_10</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0002018305813569614</v>
+        <v>0.002159191564906197</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_1</t>
+          <t>temp_lag_12</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.000195493108728671</v>
+        <v>0.00214092443296084</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>prec_x_casos_lag1</t>
+          <t>vel_vi_min_lag_4</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0001866199694072891</v>
+        <v>0.002041998089703448</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>hum_rel_lag_5</t>
+          <t>vel_vi_min_lag_8</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0001858686003476177</v>
+        <v>0.002030461863917091</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>soi_lag_10</t>
+          <t>hum_rel_lag_9</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.000185645519871984</v>
+        <v>0.002022568537737424</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_12</t>
+          <t>temp_anomalia</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0001835253742659195</v>
+        <v>0.002016826935381197</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>prec_lag_2</t>
+          <t>hum_esp_lag_2</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0001790178205604955</v>
+        <v>0.00199300189784583</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>roll_std_7</t>
+          <t>vel_vi_min_lag_6</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.0001775125570328778</v>
+        <v>0.001989473876329913</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>temp_x_tendencia</t>
+          <t>vel_vi_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.0001743905487715964</v>
+        <v>0.001977924359103867</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>soi_lag_6</t>
+          <t>prec_lag_3</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0001690328224303275</v>
+        <v>0.001970522878163749</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_8</t>
+          <t>vel_vi_max_lag_6</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.0001634917594312994</v>
+        <v>0.001957096220170844</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>hum_esp_lag_11</t>
+          <t>temp_max_anomalia</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0001624777751203375</v>
+        <v>0.00192739856766316</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>roll_mean_13</t>
+          <t>dias_lluvia</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0001611060691002938</v>
+        <v>0.001889163350601435</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>soi_lag_12</t>
+          <t>prec_lag_2</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0001598859447687412</v>
+        <v>0.001844719524325491</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>prec_lag_7</t>
+          <t>prec_lag_1</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0001597219383649968</v>
+        <v>0.001831663364504478</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>soi_lag_1</t>
+          <t>temp_lag_10</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0001586544051667384</v>
+        <v>0.001782961679518834</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>temp_min_lag_8</t>
+          <t>sst_lag_9</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.0001583507111304904</v>
+        <v>0.001762875582939366</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_7</t>
+          <t>hum_esp_lag_5</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.0001560687515809429</v>
+        <v>0.001760658941927367</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>soi_lag_2</t>
+          <t>soi_anomalia</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0001543111662591395</v>
+        <v>0.001755828853573727</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>temp</t>
+          <t>temp_lag_5</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.0001542062295462496</v>
+        <v>0.001736717033795579</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>roll_std_5</t>
+          <t>temp_lag_9</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.000153195240532924</v>
+        <v>0.001707984043408458</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>temp_min_lag_10</t>
+          <t>soi_lag_11</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0001521281757129524</v>
+        <v>0.001699476895453412</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>hum_esp_lag_1</t>
+          <t>soi_avg_6</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.0001520589226576755</v>
+        <v>0.001687708168726892</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>temp_max_lag_11</t>
+          <t>dias_lluvia_acum_4</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.0001501849570727624</v>
+        <v>0.00167860102981886</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>range_7</t>
+          <t>vel_vi_min_lag_3</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.0001485344254049684</v>
+        <v>0.001665910852796112</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>temp_max_x_tendencia</t>
+          <t>dias_lluvia_lag_1</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.0001444726320365085</v>
+        <v>0.00164739369923092</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>hum_esp_lag_8</t>
+          <t>soi_lag_12</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0001432635031952659</v>
+        <v>0.001633225652845622</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_10</t>
+          <t>prec_acum_4</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.0001396834936749184</v>
+        <v>0.001621986807756707</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>vel_vi_lag_4</t>
+          <t>vel_vi_min_lag_5</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.000139565821244038</v>
+        <v>0.001615882563563486</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>temp_max_lag_7</t>
+          <t>soi_lag_1</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.0001386481702106736</v>
+        <v>0.0016030989562245</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_12</t>
+          <t>prec</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.0001378530122110581</v>
+        <v>0.001584332687158512</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>roll_max_7</t>
+          <t>soi_max_6</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.0001348984663795404</v>
+        <v>0.00157058329493686</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>prec_lag_11</t>
+          <t>prec_lag_10</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0001330072624925598</v>
+        <v>0.00155196287279638</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sst_lag_5</t>
+          <t>vel_vi_min_lag_9</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.0001329191996494374</v>
+        <v>0.001507989397201087</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>temp_max_lag_3</t>
+          <t>temp_lag_4</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0001327683681088411</v>
+        <v>0.001484628406294006</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_2</t>
+          <t>dias_lluvia_lag_3</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.0001323705064282361</v>
+        <v>0.001456044637290142</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>hum_rel_lag_4</t>
+          <t>vel_vi_lag_11</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.0001292329788989609</v>
+        <v>0.001455938623333708</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>range_13</t>
+          <t>hum_rel_lag_8</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.0001290246627085227</v>
+        <v>0.001451293954874937</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>temp_lag_6</t>
+          <t>temp_lag_2</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.0001278748986296662</v>
+        <v>0.001448045122596136</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>temp_min_lag_4</t>
+          <t>soi_lag_10</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.000126773761155491</v>
+        <v>0.001439337919231148</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>vel_vi_lag_7</t>
+          <t>vel_vi_min_lag_11</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.0001265802107791676</v>
+        <v>0.001420523311865244</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>temp_x_casos_lag1</t>
+          <t>vel_vi_min_lag_12</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.0001246389067634661</v>
+        <v>0.001400308083173091</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_2</t>
+          <t>temp_lag_1</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.0001242521915730482</v>
+        <v>0.001383757795123294</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>temp_min</t>
+          <t>temp_min_anomalia</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.0001218321401837842</v>
+        <v>0.001374762265099885</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>acceleration</t>
+          <t>temp_lag_11</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.0001215060735005223</v>
+        <v>0.001362053597242821</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>hum_esp_lag_7</t>
+          <t>temp_max_lag_11</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.000120957777367978</v>
+        <v>0.001350920469682191</v>
       </c>
     </row>
     <row r="122">
@@ -1635,297 +1635,297 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.0001195618426705893</v>
+        <v>0.001340007514213949</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>vel_vi_lag_12</t>
+          <t>soi_lag_3</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.0001146906057217045</v>
+        <v>0.001330112392719105</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_4</t>
+          <t>prec_anomalia</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.00011458534212563</v>
+        <v>0.001312333057009745</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>sst_lag_9</t>
+          <t>hum_esp_lag_6</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.0001142699116138857</v>
+        <v>0.001304897356865445</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>hum_esp_lag_3</t>
+          <t>temp_max_lag_4</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.0001138676648428531</v>
+        <v>0.001299222212675705</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>temp_lag_1</t>
+          <t>dias_lluvia_acum_8</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.0001135304943250852</v>
+        <v>0.00128454301107684</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>soi_lag_4</t>
+          <t>hum_esp_clima_semana</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.0001122136257838714</v>
+        <v>0.001281140516945392</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_5</t>
+          <t>sst_lag_8</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.0001093248007581322</v>
+        <v>0.001278259848313552</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>temp_min_lag_9</t>
+          <t>temp_max_lag_5</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.0001053822749494188</v>
+        <v>0.001274992332203907</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>temp_lag_12</t>
+          <t>prec_lag_11</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.0001017982788147485</v>
+        <v>0.001249560763937908</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_3</t>
+          <t>prec_lag_7</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.000101235889379853</v>
+        <v>0.001231994187244697</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>temp_max_lag_4</t>
+          <t>vel_vi_max_lag_9</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.0001009440787937069</v>
+        <v>0.00122486691710543</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>vel_vi_lag_10</t>
+          <t>temp_min_lag_4</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>9.970187925963068e-05</v>
+        <v>0.001214197897012994</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>temp_lag_7</t>
+          <t>sst_lag_5</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>9.889862630961737e-05</v>
+        <v>0.001195016205869324</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>temp_lag_11</t>
+          <t>hum_rel_lag_12</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>9.637412991488431e-05</v>
+        <v>0.001155602493840051</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>roll_mean_26</t>
+          <t>vel_vi_min_anomalia</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>9.588478828360954e-05</v>
+        <v>0.001128019261927004</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>temp_max_lag_1</t>
+          <t>temp_min_lag_5</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>9.481476522327067e-05</v>
+        <v>0.001122868687634034</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>hum_rel_lag_6</t>
+          <t>hum_esp_lag_1</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>9.388010999774544e-05</v>
+        <v>0.001107351571574484</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_3</t>
+          <t>temp_min_lag_9</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>9.351849012591931e-05</v>
+        <v>0.001071479460183058</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>roll_std_13</t>
+          <t>hum_esp_lag_7</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>9.323179729247309e-05</v>
+        <v>0.001061179856697927</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>hum_esp_lag_6</t>
+          <t>soi_lag_7</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>9.29969707451335e-05</v>
+        <v>0.001043787349512374</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>sst_lag_12</t>
+          <t>temp_max_lag_12</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>9.294631752479437e-05</v>
+        <v>0.00103407456751436</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>soi_lag_7</t>
+          <t>sst_lag_7</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>9.238953765096463e-05</v>
+        <v>0.001023550468897626</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>hum_rel_lag_11</t>
+          <t>temp_max_x_prec</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>9.195320540206182e-05</v>
+        <v>0.001004558412756542</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>temp_lag_3</t>
+          <t>vel_vi_lag_10</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>9.106028528932061e-05</v>
+        <v>0.000984394424965966</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>temp_max_lag_2</t>
+          <t>vel_vi_lag_8</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>9.058895759454875e-05</v>
+        <v>0.0009820334044133244</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_12</t>
+          <t>vel_vi_lag_7</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>8.979486950821143e-05</v>
+        <v>0.0009315295408393149</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sst_lag_11</t>
+          <t>soi_lag_9</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>8.953820473791591e-05</v>
+        <v>0.0009094792468157704</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>hum_esp_lag_10</t>
+          <t>prec_lag_4</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>8.945789848287146e-05</v>
+        <v>0.0009080414289901885</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_10</t>
+          <t>vel_vi_min_lag_7</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>8.875041308439472e-05</v>
+        <v>0.0008780742633412598</v>
       </c>
     </row>
     <row r="152">
@@ -1935,487 +1935,487 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>8.861327397349782e-05</v>
+        <v>0.0008689940874727941</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>prec</t>
+          <t>vel_vi_max_lag_12</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>8.795922630451006e-05</v>
+        <v>0.0008542562096895405</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_9</t>
+          <t>vel_vi_min_lag_1</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>8.76689191639606e-05</v>
+        <v>0.0008493229071586501</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>sst_lag_6</t>
+          <t>vel_vi_max_lag_11</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>8.70835731453134e-05</v>
+        <v>0.000849076629687539</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>temp_min_lag_1</t>
+          <t>hum_rel</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>8.697394678038841e-05</v>
+        <v>0.0008489189324253613</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>hum_esp_lag_12</t>
+          <t>hum_rel_lag_1</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>8.577841786982012e-05</v>
+        <v>0.0008365018647439078</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>vel_vi_max</t>
+          <t>temp_max_lag_8</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>8.54504431518944e-05</v>
+        <v>0.0008240855548717957</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_8</t>
+          <t>temp_min_lag_8</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>8.469749711478385e-05</v>
+        <v>0.0008203431119355039</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>hum_rel_lag_2</t>
+          <t>temp_max_lag_9</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>8.444558229725354e-05</v>
+        <v>0.0008109417822854807</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>prec_lag_8</t>
+          <t>soi_lag_5</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>8.433779864965943e-05</v>
+        <v>0.0008086816244052652</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_6</t>
+          <t>vel_vi_lag_6</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>8.393993216112281e-05</v>
+        <v>0.0008042372279202512</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>roll_min_13</t>
+          <t>temp_max_clima_semana</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>8.368327749365864e-05</v>
+        <v>0.0007711506914331723</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_6</t>
+          <t>prec_lag_5</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>8.289108354339123e-05</v>
+        <v>0.0007673644110492676</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>hum_esp_lag_9</t>
+          <t>temp_lag_8</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>8.226364528137153e-05</v>
+        <v>0.0007654243623182381</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>estacionalidad_lag_4</t>
+          <t>temp_max_lag_3</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>8.192466902423496e-05</v>
+        <v>0.0007634351646029286</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>vel_vi_min</t>
+          <t>vel_vi_max_clima_semana</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>8.149195103213351e-05</v>
+        <v>0.000748023991597717</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>prec_lag_5</t>
+          <t>hum_esp</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>7.927956259965482e-05</v>
+        <v>0.0007441035449933346</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_6</t>
+          <t>vel_vi_max_lag_10</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>7.38553973937339e-05</v>
+        <v>0.000742884670938783</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>dias_lluvia</t>
+          <t>vel_vi_min_clima_semana</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7.326658025223327e-05</v>
+        <v>0.0007357293944296074</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>temp_lag_2</t>
+          <t>temp_min_lag_11</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>7.263199759895709e-05</v>
+        <v>0.000727881197778734</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>hum_esp_lag_5</t>
+          <t>dias_lluvia_lag_4</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>7.232109670438219e-05</v>
+        <v>0.000676119714529165</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>temp_max_lag_6</t>
+          <t>vel_vi_clima_semana</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>7.189273530004025e-05</v>
+        <v>0.0006714339994851958</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tendencia_lag1</t>
+          <t>temp_min_lag_7</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>6.992009729816395e-05</v>
+        <v>0.0006613393162234372</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>sst_lag_4</t>
+          <t>temp_min_lag_12</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>6.890959042618738e-05</v>
+        <v>0.000659865972894326</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>temp_min_lag_6</t>
+          <t>soi_clima_semana</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>6.710044719097023e-05</v>
+        <v>0.0006274276677589605</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>temp_min_x_casos_lag1</t>
+          <t>soi_lag_2</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>6.541450169609674e-05</v>
+        <v>0.0006014432424027151</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>vel_vi_lag_6</t>
+          <t>temp_clima_semana</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>6.536533956336761e-05</v>
+        <v>0.0005718308564992529</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>vel_vi_lag_9</t>
+          <t>dias_lluvia_lag_12</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>6.409095155142226e-05</v>
+        <v>0.0005705924174060874</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>hum_esp_lag_4</t>
+          <t>temp_max</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>6.401032548012239e-05</v>
+        <v>0.0005694536723452651</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>hum_rel_lag_8</t>
+          <t>temp_min_lag_10</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>6.323307152412652e-05</v>
+        <v>0.00055807512597236</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>temp_max_x_casos_lag1</t>
+          <t>hum_rel_clima_semana</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>6.207849575075445e-05</v>
+        <v>0.0005578691574625219</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_5</t>
+          <t>temp_min_lag_6</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>6.168934171276929e-05</v>
+        <v>0.000543259213574131</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>vel_vi_lag_5</t>
+          <t>temp_lag_6</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>5.827197197872233e-05</v>
+        <v>0.0005385257101294046</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>tendencia</t>
+          <t>vel_vi_lag_9</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>5.774074874820371e-05</v>
+        <v>0.0005325491603844352</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>prec_lag_9</t>
+          <t>hum_rel_lag_2</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>5.709133684617342e-05</v>
+        <v>0.0005278851757130396</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_8</t>
+          <t>temp_max_lag_6</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>5.701065750841583e-05</v>
+        <v>0.0004700368105705996</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_11</t>
+          <t>temp_max_lag_1</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>5.669610246423658e-05</v>
+        <v>0.0004628924661564979</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>estacionalidad_lag_20</t>
+          <t>temp_max_lag_2</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>5.56950828707368e-05</v>
+        <v>0.0004396261068266766</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>temp_min_lag_7</t>
+          <t>dias_lluvia_lag_5</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>5.485030209455243e-05</v>
+        <v>0.0004354612907243818</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>temp_min_lag_5</t>
+          <t>vel_vi_min</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>5.428073087675695e-05</v>
+        <v>0.0004342892159121546</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_4</t>
+          <t>dias_lluvia_lag_8</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>5.371503262732929e-05</v>
+        <v>0.0004172545675315081</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>hum_rel_lag_1</t>
+          <t>prec_lag_8</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>5.343739192006876e-05</v>
+        <v>0.0004082140845062311</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>temp_min_lag_11</t>
+          <t>vel_vi_min_lag_2</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>5.334881262017164e-05</v>
+        <v>0.0003623110825090302</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>sst_lag_3</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>5.227982135645554e-05</v>
+        <v>0.0003525293658418753</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>sst_lag_8</t>
+          <t>dias_lluvia_lag_6</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>4.928644024325426e-05</v>
+        <v>0.0003204479732951353</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>temp_max_lag_5</t>
+          <t>vel_vi_max_lag_8</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>4.843069799586595e-05</v>
+        <v>0.0002936154545128271</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_7</t>
+          <t>dias_lluvia_lag_10</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>4.66102216545034e-05</v>
+        <v>0.0002857494879685999</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>tendencia_lag3</t>
+          <t>dias_lluvia_lag_9</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>4.592738460315019e-05</v>
+        <v>0.0002744417163592773</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>tendencia_lag2</t>
+          <t>racha_prec_alta</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>4.586679983459113e-05</v>
+        <v>0.0002658398680737691</v>
       </c>
     </row>
     <row r="201">
@@ -2425,267 +2425,37 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>4.48677902121811e-05</v>
+        <v>0.000242398921693052</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_5</t>
+          <t>dias_lluvia_lag_2</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>4.355524044245411e-05</v>
+        <v>0.0002278833693297418</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_10</t>
+          <t>dias_lluvia_lag_7</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>4.20969210441872e-05</v>
+        <v>0.0002142569847240298</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>estacionalidad_lag_8</t>
+          <t>racha_temp_alta</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>4.172935695193588e-05</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>vel_vi</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>4.168855200053825e-05</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>temp_min_x_tendencia</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>4.094804084112282e-05</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>vel_vi_max_lag_7</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>4.040384161473043e-05</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>roll_min_7</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>4.012584737996256e-05</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>casos_dengue_lag_11</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>3.902869494393983e-05</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_1</t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>3.632327548475012e-05</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>sst_lag_7</t>
-        </is>
-      </c>
-      <c r="B211" t="n">
-        <v>3.474023411998663e-05</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>vel_vi_min_lag_9</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>3.464525018692787e-05</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>temp_min_lag_12</t>
-        </is>
-      </c>
-      <c r="B213" t="n">
-        <v>3.461872225568492e-05</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_8</t>
-        </is>
-      </c>
-      <c r="B214" t="n">
-        <v>3.440469393918939e-05</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>casos_dengue_lag_9</t>
-        </is>
-      </c>
-      <c r="B215" t="n">
-        <v>3.296435400778118e-05</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_7</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>2.788974240434695e-05</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>estacionalidad_lag_16</t>
-        </is>
-      </c>
-      <c r="B217" t="n">
-        <v>2.585302789480918e-05</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>hum_rel_lag_7</t>
-        </is>
-      </c>
-      <c r="B218" t="n">
-        <v>2.533456611991474e-05</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>casos_dengue_lag_1</t>
-        </is>
-      </c>
-      <c r="B219" t="n">
-        <v>2.193864888957451e-05</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>roll_max_26</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>2.161463356176848e-05</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>roll_max_13</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>2.036590700003654e-05</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>temp_max_lag_8</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>1.550283774346165e-05</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_12</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>1.529099984290612e-05</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>estacionalidad_lag_12</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
-        <v>1.356395890263685e-05</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>roll_min_26</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
-        <v>9.087576323314955e-06</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>es_pico_lag1</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>1.774247614854796e-06</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>es_pico_lag2</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>3.079941338379437e-07</v>
+        <v>1.902779994972879e-05</v>
       </c>
     </row>
   </sheetData>

--- a/3_resultados/atributos_seleccionados_rf.xlsx
+++ b/3_resultados/atributos_seleccionados_rf.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B204"/>
+  <dimension ref="A1:B184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,121 +431,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hum_esp_anomalia</t>
+          <t>dias_lluvia_acum_12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2452845064278026</v>
+        <v>0.1661232715056245</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>soi_min_12</t>
+          <t>soi_avg_12</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1285701341627864</v>
+        <v>0.127077546582333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sst_max_12</t>
+          <t>vel_vi_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1176533921921825</v>
+        <v>0.04387435568055947</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sst_min_6</t>
+          <t>vel_vi_max_lag_1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03361814080524847</v>
+        <v>0.03647031317602601</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sst_anomalia</t>
+          <t>hum_esp_lag_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02181639622129038</v>
+        <v>0.03249522341984165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hum_esp_lag_12</t>
+          <t>hum_esp_lag_10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01515302359345671</v>
+        <v>0.02730634231467241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dias_lluvia_acum_12</t>
+          <t>hum_esp_lag_9</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01442572469180154</v>
+        <v>0.02642369860331386</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hum_rel_anomalia</t>
+          <t>hum_esp_lag_6</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01148631850764395</v>
+        <v>0.02552241188387218</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>temp_min</t>
+          <t>sst_avg_12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0108662615542897</v>
+        <v>0.02537557096429799</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hum_esp_lag_10</t>
+          <t>hum_esp_lag_7</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009505468917428156</v>
+        <v>0.02349437719954523</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hum_esp_lag_8</t>
+          <t>vel_vi_max_lag_4</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.008677139247650199</v>
+        <v>0.02305972521691087</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>temp_min_clima_semana</t>
+          <t>hum_esp_lag_8</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008240012188213849</v>
+        <v>0.02098692581864348</v>
       </c>
     </row>
     <row r="14">
@@ -555,1907 +555,1707 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.008152559223626609</v>
+        <v>0.01859920305463887</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hum_esp_lag_11</t>
+          <t>sst_anomalia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.007504213171040419</v>
+        <v>0.0177419375618928</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>prec_acum_12</t>
+          <t>hum_esp_lag_4</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.006006343264881317</v>
+        <v>0.01564779276563884</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>soi_avg_12</t>
+          <t>hum_esp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.005962988323023764</v>
+        <v>0.01340295700407719</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hum_esp_lag_9</t>
+          <t>vel_vi_max_lag_3</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.005636035472276488</v>
+        <v>0.01293738512488906</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_4</t>
+          <t>vel_vi_max_lag_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.00555672713961146</v>
+        <v>0.01293472301371699</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>vel_vi_lag_1</t>
+          <t>hum_esp_lag_3</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.005534504429852833</v>
+        <v>0.01199879623063078</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>soi_max_12</t>
+          <t>hum_rel_lag_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.005228486715612235</v>
+        <v>0.01092395537692268</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hum_rel_lag_4</t>
+          <t>sst_avg_6</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.00515350430940334</v>
+        <v>0.01000506689710486</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>temp_min_lag_2</t>
+          <t>prec_acum_12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.005088786949914433</v>
+        <v>0.008676914668331429</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hum_rel_lag_6</t>
+          <t>sst_lag_11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.005035913642323949</v>
+        <v>0.008402306528199059</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sst_lag_1</t>
+          <t>sst_lag_2</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.005021049695016376</v>
+        <v>0.008174348600067223</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prec_clima_semana</t>
+          <t>sst_lag_12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.004937245663832282</v>
+        <v>0.007900547279121328</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_10</t>
+          <t>sst_lag_1</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.004797770184422227</v>
+        <v>0.00756855436922691</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>soi_lag_6</t>
+          <t>dias_lluvia_acum_8</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.004706624955176446</v>
+        <v>0.006683707583397961</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sst_lag_12</t>
+          <t>hum_esp_lag_2</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.004493595162676285</v>
+        <v>0.006632182646259902</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>temp_max_lag_10</t>
+          <t>sst_lag_4</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.004374787283289443</v>
+        <v>0.006619845269310084</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>prec_acum_8</t>
+          <t>sst_lag_5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.004306280782017992</v>
+        <v>0.006589910186197367</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hum_rel_lag_5</t>
+          <t>vel_vi_lag_1</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.004301884234647948</v>
+        <v>0.005953783033450456</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>temp_min_lag_1</t>
+          <t>vel_vi_max_lag_2</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.004298348489679546</v>
+        <v>0.005857649761584128</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sst_min_12</t>
+          <t>vel_vi_lag_3</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.004281580648783155</v>
+        <v>0.005767338542929855</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sst_avg_6</t>
+          <t>vel_vi_max_anomalia</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.004157756965387886</v>
+        <v>0.005152243978934355</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_5</t>
+          <t>hum_esp_lag_12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.004111586934946371</v>
+        <v>0.005033210617098872</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>temp_min_lag_3</t>
+          <t>sst_lag_6</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.004087841567016287</v>
+        <v>0.004747757097545236</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sst_lag_11</t>
+          <t>temp_min_lag_1</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.004022661495818723</v>
+        <v>0.004693118517094431</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>vel_vi_lag_2</t>
+          <t>sst_lag_3</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.003924491986934801</v>
+        <v>0.00453581184264614</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hum_esp_lag_3</t>
+          <t>sst_lag_10</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.003893154020255264</v>
+        <v>0.00442845587628677</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_1</t>
+          <t>vel_vi_lag_2</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.003827595963803719</v>
+        <v>0.004356223160482727</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_3</t>
+          <t>sst_lag_9</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.00368921964390608</v>
+        <v>0.004329561376966672</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_7</t>
+          <t>hum_rel_anomalia</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.00359557106558031</v>
+        <v>0.003864180542858748</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sst_max_6</t>
+          <t>hum_esp_lag_1</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.003589566138529125</v>
+        <v>0.003787389209540416</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sst_avg_12</t>
+          <t>sst_lag_8</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.00344936758942197</v>
+        <v>0.00373280172728787</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>prec_lag_12</t>
+          <t>soi_lag_6</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.003333137613651332</v>
+        <v>0.003676507666101832</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>vel_vi_max_anomalia</t>
+          <t>temp_min_lag_2</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.003332202256076602</v>
+        <v>0.003437479103283641</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>indice_vectorial</t>
+          <t>hum_esp_lag_11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.003043035471158356</v>
+        <v>0.003293531211470234</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>temp_lag_3</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.002898372884916107</v>
+        <v>0.003028019728369692</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>temp_x_hum_rel</t>
+          <t>temp_min</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.002874888966278785</v>
+        <v>0.002909045368723186</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_2</t>
+          <t>temp_lag_1</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.002830992214398192</v>
+        <v>0.002899575317073994</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>vel_vi_lag_3</t>
+          <t>temp_lag_10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.002824584858872356</v>
+        <v>0.002891769394521402</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>soi_min_6</t>
+          <t>vel_vi_min_lag_9</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.002817446645603709</v>
+        <v>0.002755681273123281</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sst_lag_2</t>
+          <t>racha_temp_alta</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.002803587089717393</v>
+        <v>0.002738414454447869</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>vel_vi_lag_4</t>
+          <t>temp_x_hum_rel</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.002784325459797237</v>
+        <v>0.002730252239952225</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sst_clima_semana</t>
+          <t>soi_lag_5</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.002760185995217932</v>
+        <v>0.002651510764941873</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>hum_rel_lag_7</t>
+          <t>vel_vi_max_lag_7</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.002745154669796634</v>
+        <v>0.002621742598440842</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>prec_lag_9</t>
+          <t>vel_vi_max_lag_6</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.002740985874259597</v>
+        <v>0.002617132156166292</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>soi_lag_4</t>
+          <t>soi_avg_6</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.002697534543141464</v>
+        <v>0.002597844523425691</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>prec_lag_6</t>
+          <t>temp_min_lag_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.002663533441884066</v>
+        <v>0.002588419627693923</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>vel_vi_lag_12</t>
+          <t>vel_vi_lag_4</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.002627957013868101</v>
+        <v>0.002568522638264227</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>temp_max_lag_7</t>
+          <t>temp_min_lag_3</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.002560078641779013</v>
+        <v>0.002386749040949209</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>vel_vi</t>
+          <t>vel_vi_min_lag_10</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.002550534711862848</v>
+        <v>0.002314512565953601</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>hum_esp_lag_4</t>
+          <t>vel_vi_lag_11</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.002476570592922779</v>
+        <v>0.002203875123369178</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>sst_lag_3</t>
+          <t>sst_lag_7</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0024746764390075</v>
+        <v>0.002177370730651267</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>sst_lag_10</t>
+          <t>temp_max_anomalia</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.002456355423861834</v>
+        <v>0.002162863210706705</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>temp_lag_7</t>
+          <t>hum_rel_lag_12</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.002393648185416407</v>
+        <v>0.002057993517753778</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>vel_vi_lag_5</t>
+          <t>temp_anomalia</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.002368136395619907</v>
+        <v>0.002030870613592107</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>hum_rel_lag_11</t>
+          <t>vel_vi_min_lag_3</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.002286571565678055</v>
+        <v>0.001953250117294103</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dias_lluvia_anomalia</t>
+          <t>hum_rel_lag_6</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.002276211187671515</v>
+        <v>0.001911005734208947</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>sst_lag_4</t>
+          <t>hum_rel_lag_1</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.002256496350610852</v>
+        <v>0.00186876351709191</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>vel_vi_anomalia</t>
+          <t>prec_acum_8</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.002229891475395674</v>
+        <v>0.00181254143372824</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dias_lluvia_clima_semana</t>
+          <t>vel_vi_max_lag_9</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.002217381841542494</v>
+        <v>0.001780778418819421</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>soi</t>
+          <t>vel_vi</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.00218360734380389</v>
+        <v>0.00176888864908837</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>sst_lag_6</t>
+          <t>temp_min_lag_4</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.002169151576791163</v>
+        <v>0.001705748799073401</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>hum_rel_lag_10</t>
+          <t>soi_lag_8</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.002159191564906197</v>
+        <v>0.001665961710489829</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>temp_lag_12</t>
+          <t>hum_rel_lag_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.00214092443296084</v>
+        <v>0.001622099164176744</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_4</t>
+          <t>soi_lag_9</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.002041998089703448</v>
+        <v>0.00157039886023782</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_8</t>
+          <t>temp_lag_4</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.002030461863917091</v>
+        <v>0.001502437742497727</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>hum_rel_lag_9</t>
+          <t>vel_vi_min_lag_7</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.002022568537737424</v>
+        <v>0.001495933884512698</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>temp_anomalia</t>
+          <t>soi_lag_10</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.002016826935381197</v>
+        <v>0.001447821102653806</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>hum_esp_lag_2</t>
+          <t>prec_lag_12</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.00199300189784583</v>
+        <v>0.001398953914016152</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_6</t>
+          <t>vel_vi_lag_10</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.001989473876329913</v>
+        <v>0.001389342927190997</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>vel_vi_max</t>
+          <t>temp_lag_7</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.001977924359103867</v>
+        <v>0.001387921326340973</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>prec_lag_3</t>
+          <t>temp_min_anomalia</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.001970522878163749</v>
+        <v>0.00137965558465809</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_6</t>
+          <t>temp_min_lag_6</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.001957096220170844</v>
+        <v>0.001373744930742634</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>temp_max_anomalia</t>
+          <t>vel_vi_lag_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.00192739856766316</v>
+        <v>0.001361784949643263</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>dias_lluvia</t>
+          <t>vel_vi_anomalia</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.001889163350601435</v>
+        <v>0.001360663827688795</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>prec_lag_2</t>
+          <t>vel_vi_min_lag_8</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.001844719524325491</v>
+        <v>0.00134635813328114</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>prec_lag_1</t>
+          <t>soi_lag_7</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.001831663364504478</v>
+        <v>0.001317225646589783</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>temp_lag_10</t>
+          <t>vel_vi_lag_12</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.001782961679518834</v>
+        <v>0.001302333846312584</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>sst_lag_9</t>
+          <t>temp_max_lag_4</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.001762875582939366</v>
+        <v>0.001282419243897124</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>hum_esp_lag_5</t>
+          <t>vel_vi_max_lag_8</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.001760658941927367</v>
+        <v>0.001278127332901513</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>soi_anomalia</t>
+          <t>temp_lag_3</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.001755828853573727</v>
+        <v>0.001275776816469449</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>temp_lag_5</t>
+          <t>vel_vi_min_lag_2</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.001736717033795579</v>
+        <v>0.001249293981623039</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>temp_lag_9</t>
+          <t>temp_lag_5</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.001707984043408458</v>
+        <v>0.001234236760043881</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>soi_lag_11</t>
+          <t>temp_min_lag_11</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.001699476895453412</v>
+        <v>0.001231291079863068</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>soi_avg_6</t>
+          <t>temp_min_lag_9</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.001687708168726892</v>
+        <v>0.001218491324938468</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>dias_lluvia_acum_4</t>
+          <t>vel_vi_max_lag_12</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.00167860102981886</v>
+        <v>0.001183122627746071</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_3</t>
+          <t>vel_vi_min_lag_12</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.001665910852796112</v>
+        <v>0.001164558593077816</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_1</t>
+          <t>soi_lag_12</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.00164739369923092</v>
+        <v>0.00115271285694611</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>soi_lag_12</t>
+          <t>temp_max_lag_2</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.001633225652845622</v>
+        <v>0.001151002236524745</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>prec_acum_4</t>
+          <t>vel_vi_min_lag_6</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.001621986807756707</v>
+        <v>0.001139728434522904</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_5</t>
+          <t>soi_lag_4</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.001615882563563486</v>
+        <v>0.001138195357728532</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>soi_lag_1</t>
+          <t>temp_min_lag_8</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.0016030989562245</v>
+        <v>0.001132309274977998</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>prec</t>
+          <t>prec_lag_9</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.001584332687158512</v>
+        <v>0.001116643941862091</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>soi_max_6</t>
+          <t>soi_lag_1</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.00157058329493686</v>
+        <v>0.001116299362892974</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>prec_lag_10</t>
+          <t>vel_vi_lag_8</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.00155196287279638</v>
+        <v>0.0010977689653534</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_9</t>
+          <t>soi_lag_3</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.001507989397201087</v>
+        <v>0.001094689319590702</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>temp_lag_4</t>
+          <t>temp_lag_2</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.001484628406294006</v>
+        <v>0.001085707594227331</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_3</t>
+          <t>hum_rel</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.001456044637290142</v>
+        <v>0.001063814158243455</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>vel_vi_lag_11</t>
+          <t>temp_max</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.001455938623333708</v>
+        <v>0.001023469223565644</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>hum_rel_lag_8</t>
+          <t>prec_lag_5</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.001451293954874937</v>
+        <v>0.001011595242454804</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>temp_lag_2</t>
+          <t>soi_lag_11</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.001448045122596136</v>
+        <v>0.001008216059169757</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>soi_lag_10</t>
+          <t>temp_min_lag_10</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.001439337919231148</v>
+        <v>0.001001164242518304</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_11</t>
+          <t>vel_vi_max_lag_10</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.001420523311865244</v>
+        <v>0.0009501461481177242</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_12</t>
+          <t>hum_esp_anomalia</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.001400308083173091</v>
+        <v>0.0009291581946373492</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>temp_lag_1</t>
+          <t>soi_anomalia</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.001383757795123294</v>
+        <v>0.0009252189316487432</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>temp_min_anomalia</t>
+          <t>vel_vi_min_lag_5</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.001374762265099885</v>
+        <v>0.0009168709574960556</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>temp_lag_11</t>
+          <t>vel_vi_lag_9</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.001362053597242821</v>
+        <v>0.0009132643001639813</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>temp_max_lag_11</t>
+          <t>prec_acum_4</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.001350920469682191</v>
+        <v>0.0009083096198271417</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>hum_rel_lag_3</t>
+          <t>temp_min_lag_7</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.001340007514213949</v>
+        <v>0.000905690254959588</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>soi_lag_3</t>
+          <t>vel_vi_min_lag_11</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.001330112392719105</v>
+        <v>0.0008899389902701581</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>prec_anomalia</t>
+          <t>soi_lag_2</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.001312333057009745</v>
+        <v>0.0008822117024825131</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>hum_esp_lag_6</t>
+          <t>indice_vectorial</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.001304897356865445</v>
+        <v>0.0008819526720775946</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>temp_max_lag_4</t>
+          <t>temp_max_lag_1</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.001299222212675705</v>
+        <v>0.0008644269576302617</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>dias_lluvia_acum_8</t>
+          <t>temp_lag_9</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.00128454301107684</v>
+        <v>0.0008624135510387141</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>hum_esp_clima_semana</t>
+          <t>temp_lag_11</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.001281140516945392</v>
+        <v>0.0008566022826626033</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>sst_lag_8</t>
+          <t>soi</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.001278259848313552</v>
+        <v>0.0008528375073485182</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>temp_max_lag_5</t>
+          <t>hum_rel_lag_2</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.001274992332203907</v>
+        <v>0.0008320151915390294</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>prec_lag_11</t>
+          <t>temp_lag_8</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.001249560763937908</v>
+        <v>0.0008160560810211666</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>prec_lag_7</t>
+          <t>vel_vi_lag_7</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.001231994187244697</v>
+        <v>0.0008114739849190978</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_9</t>
+          <t>prec_lag_6</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.00122486691710543</v>
+        <v>0.0007933193664255876</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>temp_min_lag_4</t>
+          <t>temp_max_lag_7</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.001214197897012994</v>
+        <v>0.0007868472990651439</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sst_lag_5</t>
+          <t>vel_vi_max_lag_11</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.001195016205869324</v>
+        <v>0.0007807780881375216</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>hum_rel_lag_12</t>
+          <t>vel_vi_lag_6</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.001155602493840051</v>
+        <v>0.0007759617895225264</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>vel_vi_min_anomalia</t>
+          <t>hum_rel_lag_7</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.001128019261927004</v>
+        <v>0.0007094368023481185</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>temp_min_lag_5</t>
+          <t>vel_vi_min</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.001122868687634034</v>
+        <v>0.0007075855152505837</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>hum_esp_lag_1</t>
+          <t>hum_rel_lag_8</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.001107351571574484</v>
+        <v>0.0007056580210879641</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>temp_min_lag_9</t>
+          <t>hum_rel_lag_3</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.001071479460183058</v>
+        <v>0.0006982498300283033</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>hum_esp_lag_7</t>
+          <t>prec_lag_4</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.001061179856697927</v>
+        <v>0.0006889557309732284</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>soi_lag_7</t>
+          <t>vel_vi_min_anomalia</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.001043787349512374</v>
+        <v>0.000672596046900557</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>temp_max_lag_12</t>
+          <t>temp_max_lag_10</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.00103407456751436</v>
+        <v>0.0006679756520901791</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>sst_lag_7</t>
+          <t>temp_max_lag_5</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.001023550468897626</v>
+        <v>0.0006493236974770872</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>temp_max_x_prec</t>
+          <t>vel_vi_min_lag_4</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.001004558412756542</v>
+        <v>0.0006217704532763018</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>vel_vi_lag_10</t>
+          <t>prec_lag_3</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.000984394424965966</v>
+        <v>0.0006040236686046579</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>vel_vi_lag_8</t>
+          <t>dias_lluvia_acum_4</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.0009820334044133244</v>
+        <v>0.0005891705677899901</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>vel_vi_lag_7</t>
+          <t>temp_max_lag_9</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.0009315295408393149</v>
+        <v>0.0005870200535884486</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>soi_lag_9</t>
+          <t>temp_max_lag_3</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.0009094792468157704</v>
+        <v>0.0005862447776927711</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>prec_lag_4</t>
+          <t>temp_min_lag_12</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.0009080414289901885</v>
+        <v>0.0005834450608605491</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_7</t>
+          <t>vel_vi_min_lag_1</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.0008780742633412598</v>
+        <v>0.0005729965746360242</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>soi_lag_8</t>
+          <t>temp_max_lag_6</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.0008689940874727941</v>
+        <v>0.0005591834946287586</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_12</t>
+          <t>prec_lag_2</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.0008542562096895405</v>
+        <v>0.0005533546103673855</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_1</t>
+          <t>prec_anomalia</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.0008493229071586501</v>
+        <v>0.0005434185254260858</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_11</t>
+          <t>prec_lag_8</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.000849076629687539</v>
+        <v>0.0005416934525317962</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>hum_rel</t>
+          <t>prec_lag_7</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.0008489189324253613</v>
+        <v>0.0005309510958678469</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>hum_rel_lag_1</t>
+          <t>temp_max_lag_12</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.0008365018647439078</v>
+        <v>0.000513030746861165</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>temp_max_lag_8</t>
+          <t>temp_max_lag_11</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.0008240855548717957</v>
+        <v>0.0005116737178264113</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>temp_min_lag_8</t>
+          <t>hum_rel_lag_11</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.0008203431119355039</v>
+        <v>0.0004974582123202442</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>temp_max_lag_9</t>
+          <t>prec_lag_1</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.0008109417822854807</v>
+        <v>0.0004954366225470804</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>soi_lag_5</t>
+          <t>temp_max_x_prec</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.0008086816244052652</v>
+        <v>0.000474458044311109</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>vel_vi_lag_6</t>
+          <t>hum_rel_lag_10</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.0008042372279202512</v>
+        <v>0.0004593903246893435</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>temp_max_clima_semana</t>
+          <t>temp_max_lag_8</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.0007711506914331723</v>
+        <v>0.0004041093901511636</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>prec_lag_5</t>
+          <t>temp_lag_6</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.0007673644110492676</v>
+        <v>0.0003938744120342192</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>temp_lag_8</t>
+          <t>dias_lluvia_lag_5</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.0007654243623182381</v>
+        <v>0.0003927406011087633</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>temp_max_lag_3</t>
+          <t>dias_lluvia_lag_4</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.0007634351646029286</v>
+        <v>0.0003878081597821979</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>vel_vi_max_clima_semana</t>
+          <t>prec_lag_10</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.000748023991597717</v>
+        <v>0.0003459305381135765</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>hum_esp</t>
+          <t>dias_lluvia_lag_8</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.0007441035449933346</v>
+        <v>0.0003437907662107346</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_10</t>
+          <t>dias_lluvia_anomalia</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.000742884670938783</v>
+        <v>0.0003410704871792485</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>vel_vi_min_clima_semana</t>
+          <t>hum_rel_lag_9</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.0007357293944296074</v>
+        <v>0.0003333775857176349</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>temp_min_lag_11</t>
+          <t>prec</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.000727881197778734</v>
+        <v>0.0003184574698216747</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_4</t>
+          <t>dias_lluvia_lag_12</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.000676119714529165</v>
+        <v>0.0003021482504789523</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>vel_vi_clima_semana</t>
+          <t>dias_lluvia</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.0006714339994851958</v>
+        <v>0.0002936777848734199</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>temp_min_lag_7</t>
+          <t>dias_lluvia_lag_10</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.0006613393162234372</v>
+        <v>0.0002852588366323469</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>temp_min_lag_12</t>
+          <t>dias_lluvia_lag_3</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.000659865972894326</v>
+        <v>0.0002654426504630956</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>soi_clima_semana</t>
+          <t>dias_lluvia_lag_11</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.0006274276677589605</v>
+        <v>0.0002477255897512508</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>soi_lag_2</t>
+          <t>temp_lag_12</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.0006014432424027151</v>
+        <v>0.0002311540222093912</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>temp_clima_semana</t>
+          <t>prec_lag_11</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.0005718308564992529</v>
+        <v>0.0002304181767611424</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>dias_lluvia_lag_12</t>
+          <t>dias_lluvia_lag_2</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.0005705924174060874</v>
+        <v>0.0002080020345825976</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>temp_max</t>
+          <t>dias_lluvia_lag_7</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.0005694536723452651</v>
+        <v>0.0001884768812188457</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>temp_min_lag_10</t>
+          <t>dias_lluvia_lag_9</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.00055807512597236</v>
+        <v>0.0001884566155375892</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>hum_rel_clima_semana</t>
+          <t>dias_lluvia_lag_1</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.0005578691574625219</v>
+        <v>0.0001878989955587694</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>temp_min_lag_6</t>
+          <t>dias_lluvia_lag_6</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.000543259213574131</v>
+        <v>0.0001343285949555784</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>temp_lag_6</t>
+          <t>racha_prec_alta</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.0005385257101294046</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>vel_vi_lag_9</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>0.0005325491603844352</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>hum_rel_lag_2</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>0.0005278851757130396</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>temp_max_lag_6</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>0.0004700368105705996</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>temp_max_lag_1</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>0.0004628924661564979</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>temp_max_lag_2</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>0.0004396261068266766</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_5</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>0.0004354612907243818</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>vel_vi_min</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>0.0004342892159121546</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_8</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>0.0004172545675315081</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>prec_lag_8</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>0.0004082140845062311</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>vel_vi_min_lag_2</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>0.0003623110825090302</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>temp</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>0.0003525293658418753</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_6</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>0.0003204479732951353</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>vel_vi_max_lag_8</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>0.0002936154545128271</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_10</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>0.0002857494879685999</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_9</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>0.0002744417163592773</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>racha_prec_alta</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>0.0002658398680737691</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_11</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>0.000242398921693052</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_2</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>0.0002278833693297418</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>dias_lluvia_lag_7</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>0.0002142569847240298</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>racha_temp_alta</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>1.902779994972879e-05</v>
+        <v>0.0001125040554614257</v>
       </c>
     </row>
   </sheetData>
